--- a/multi/det_gpt_domain.xlsx
+++ b/multi/det_gpt_domain.xlsx
@@ -327,7 +327,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="30.800000000000004" min="1" max="1" bestFit="1" customWidth="1"/>
@@ -442,20 +442,20 @@
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t>manufacturing_tomaskova_4</t>
+          <t>manufacturing_lodhi_5</t>
         </is>
       </c>
       <c r="B9" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0.1</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t>tourism_bpmai_1</t>
+          <t>manufacturing_tomaskova_4</t>
         </is>
       </c>
       <c r="B10" s="0" t="n">
@@ -468,7 +468,7 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t>tourism_corradini_2</t>
+          <t>tourism_bpmai_1</t>
         </is>
       </c>
       <c r="B11" s="0" t="n">
@@ -481,7 +481,7 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t>tourism_fouad_3</t>
+          <t>tourism_corradini_2</t>
         </is>
       </c>
       <c r="B12" s="0" t="n">
@@ -494,13 +494,26 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
+          <t>tourism_fouad_3</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
           <t>tourism_web_5</t>
         </is>
       </c>
-      <c r="B13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="0" t="n">
+      <c r="B14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="0" t="n">
         <v>0.1</v>
       </c>
     </row>

--- a/multi/det_gpt_domain.xlsx
+++ b/multi/det_gpt_domain.xlsx
@@ -433,10 +433,10 @@
         </is>
       </c>
       <c r="B8" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -446,10 +446,10 @@
         </is>
       </c>
       <c r="B9" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0.0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
